--- a/playwright poc/data/excel/tests/User_Test_Cases.xlsx
+++ b/playwright poc/data/excel/tests/User_Test_Cases.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>ID</t>
   </si>
@@ -49,10 +49,10 @@
     <t>Expected data</t>
   </si>
   <si>
-    <t>flowKey</t>
-  </si>
-  <si>
-    <t>TC-USER-01</t>
+    <t>flowCode</t>
+  </si>
+  <si>
+    <t>TC-USER-CREATE-01</t>
   </si>
   <si>
     <t>user</t>
@@ -83,10 +83,10 @@
     <t>{"success":true}</t>
   </si>
   <si>
-    <t>createUser</t>
-  </si>
-  <si>
-    <t>TC-USER-02</t>
+    <t>create</t>
+  </si>
+  <si>
+    <t>TC-USER-DELETE-USER-02</t>
   </si>
   <si>
     <t>Delete user</t>
@@ -107,10 +107,10 @@
     <t>{"success":true,"message":"User has been successfully"}</t>
   </si>
   <si>
-    <t>deleteUser</t>
-  </si>
-  <si>
-    <t>TC-USER-03</t>
+    <t>delete</t>
+  </si>
+  <si>
+    <t>TC-USER-EDIT-USER-PASS-03</t>
   </si>
   <si>
     <t>Edit user password</t>
@@ -134,7 +134,22 @@
     <t>{"success":true,"message":"Password has been"}</t>
   </si>
   <si>
-    <t>editUserPassword</t>
+    <t>edituserpass</t>
+  </si>
+  <si>
+    <t>TC-USER-SEARCH-PHY-04</t>
+  </si>
+  <si>
+    <t>Search Pysicians</t>
+  </si>
+  <si>
+    <t>naviagte to phycisians and search for doc</t>
+  </si>
+  <si>
+    <t>{"searchName":"Lokid"}</t>
+  </si>
+  <si>
+    <t>search</t>
   </si>
 </sst>
 </file>
@@ -481,10 +496,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="22.862142857142857" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -493,9 +508,9 @@
     <col min="7" max="7" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="2" width="164.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="23.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -650,6 +665,44 @@
         <v>39</v>
       </c>
     </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
